--- a/AfterToken/Configs/GameConfig/Datas/enemy.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/enemy.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -488,6 +488,11 @@
           <t>chaseRange</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>radius</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -550,6 +555,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -610,6 +620,11 @@
       <c r="L3" t="inlineStr">
         <is>
           <t>仇恨范围（追击触发距离）</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>碰撞/寻路膨胀半径（米）</t>
         </is>
       </c>
     </row>
@@ -651,6 +666,9 @@
       <c r="L4" t="n">
         <v>5</v>
       </c>
+      <c r="M4" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -689,6 +707,9 @@
       </c>
       <c r="L5" t="n">
         <v>5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/AfterToken/Configs/GameConfig/Datas/enemy.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/enemy.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -493,6 +493,11 @@
           <t>radius</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>pursuitRange</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -560,6 +565,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -619,12 +629,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>仇恨范围（追击触发距离）</t>
+          <t>检测距离（米）：玩家进入此距离触发追击</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>碰撞/寻路膨胀半径（米）</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>追踪范围（米）：追击状态下玩家超过此距离则丢失目标</t>
         </is>
       </c>
     </row>
@@ -669,6 +684,9 @@
       <c r="M4" t="n">
         <v>0.3</v>
       </c>
+      <c r="N4" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -710,6 +728,9 @@
       </c>
       <c r="M5" t="n">
         <v>0.3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
